--- a/templates/samples/SALES_BM_SAMPLE.xlsx
+++ b/templates/samples/SALES_BM_SAMPLE.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -507,34 +507,34 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B3" t="str">
-        <v>BM-5005</v>
+        <v>BM-5006</v>
       </c>
       <c r="C3" t="str">
-        <v>SAM-128GB-MID</v>
+        <v>SAM-256GB-WHI</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000039595</v>
+        <v>350100000047514</v>
       </c>
       <c r="E3" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>261.54</v>
+        <v>446.53</v>
       </c>
       <c r="H3">
-        <v>391.67</v>
+        <v>643.55</v>
       </c>
       <c r="I3" t="str">
-        <v>Card</v>
+        <v>Paypal</v>
       </c>
       <c r="J3">
-        <v>130.13</v>
+        <v>197.01999999999998</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="N3">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -560,34 +560,34 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-12</v>
       </c>
       <c r="B4" t="str">
-        <v>BM-5009</v>
+        <v>BM-5011</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-256GB-BLA</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000071271</v>
+        <v>350100000087109</v>
       </c>
       <c r="E4" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>229.85</v>
+        <v>514.23</v>
       </c>
       <c r="H4">
-        <v>339.76</v>
+        <v>704.32</v>
       </c>
       <c r="I4" t="str">
-        <v>Paypal</v>
+        <v>Card</v>
       </c>
       <c r="J4">
-        <v>109.91</v>
+        <v>190.09000000000003</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="N4">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -613,16 +613,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B5" t="str">
-        <v>BM-5013</v>
+        <v>BM-5016</v>
       </c>
       <c r="C5" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>IPH-64GB-MID</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000102947</v>
+        <v>350100000126704</v>
       </c>
       <c r="E5" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -631,16 +631,16 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>230.57</v>
+        <v>212.15</v>
       </c>
       <c r="H5">
-        <v>319.34</v>
+        <v>302.32</v>
       </c>
       <c r="I5" t="str">
-        <v>Klarna</v>
+        <v>Card</v>
       </c>
       <c r="J5">
-        <v>88.76999999999998</v>
+        <v>90.16999999999999</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -666,34 +666,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-22</v>
       </c>
       <c r="B6" t="str">
-        <v>BM-5017</v>
+        <v>BM-5021</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-128GB-GRA</v>
+        <v>SAM-128GB-BLU</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000134623</v>
+        <v>350100000166299</v>
       </c>
       <c r="E6" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>219.35</v>
+        <v>246.31</v>
       </c>
       <c r="H6">
-        <v>312.58</v>
+        <v>323.35</v>
       </c>
       <c r="I6" t="str">
-        <v>Card</v>
+        <v>Klarna</v>
       </c>
       <c r="J6">
-        <v>93.22999999999999</v>
+        <v>77.04000000000002</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -719,34 +719,34 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B7" t="str">
-        <v>BM-5021</v>
+        <v>BM-5026</v>
       </c>
       <c r="C7" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>IPH-128GB-PUR</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000166299</v>
+        <v>350100000205894</v>
       </c>
       <c r="E7" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>246.31</v>
+        <v>325.88</v>
       </c>
       <c r="H7">
-        <v>322.89</v>
+        <v>448.08</v>
       </c>
       <c r="I7" t="str">
-        <v>Klarna</v>
+        <v>Card</v>
       </c>
       <c r="J7">
-        <v>76.57999999999998</v>
+        <v>122.19999999999999</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -772,34 +772,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B8" t="str">
-        <v>BM-5025</v>
+        <v>BM-5031</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-128GB-STA</v>
+        <v>GOO-128GB-GRE</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000197975</v>
+        <v>350100000245489</v>
       </c>
       <c r="E8" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>233.36</v>
+        <v>290.37</v>
       </c>
       <c r="H8">
-        <v>340.98</v>
+        <v>415.64</v>
       </c>
       <c r="I8" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J8">
-        <v>107.62</v>
+        <v>125.26999999999998</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -825,34 +825,34 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B9" t="str">
-        <v>BM-5029</v>
+        <v>BM-5036</v>
       </c>
       <c r="C9" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>SAM-128GB-GRE</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000229651</v>
+        <v>350100000293003</v>
       </c>
       <c r="E9" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>253.86</v>
+        <v>262.94</v>
       </c>
       <c r="H9">
-        <v>368.99</v>
+        <v>388.08</v>
       </c>
       <c r="I9" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J9">
-        <v>115.13</v>
+        <v>125.13999999999999</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -878,34 +878,34 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B10" t="str">
-        <v>BM-5033</v>
+        <v>BM-5041</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-128GB-GRE</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000261327</v>
+        <v>350100000324679</v>
       </c>
       <c r="E10" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>209.59</v>
+        <v>232.24</v>
       </c>
       <c r="H10">
-        <v>300.01</v>
+        <v>310.64</v>
       </c>
       <c r="I10" t="str">
-        <v>Klarna</v>
+        <v>Paypal</v>
       </c>
       <c r="J10">
-        <v>90.41999999999999</v>
+        <v>78.39999999999998</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -917,7 +917,7 @@
         <v/>
       </c>
       <c r="N10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -931,16 +931,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B11" t="str">
-        <v>BM-5037</v>
+        <v>BM-5046</v>
       </c>
       <c r="C11" t="str">
-        <v>SAM-128GB-GRE</v>
+        <v>SAM-256GB-PUR</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000293003</v>
+        <v>350100000364274</v>
       </c>
       <c r="E11" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -949,16 +949,16 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>262.94</v>
+        <v>453.75</v>
       </c>
       <c r="H11">
-        <v>359.97</v>
+        <v>609.97</v>
       </c>
       <c r="I11" t="str">
-        <v>Card</v>
+        <v>Klarna</v>
       </c>
       <c r="J11">
-        <v>97.03000000000003</v>
+        <v>156.22000000000003</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -984,16 +984,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B12" t="str">
-        <v>BM-5041</v>
+        <v>BM-5051</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-128GB-MID</v>
+        <v>IPH-256GB-GRE</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000324679</v>
+        <v>350100000403869</v>
       </c>
       <c r="E12" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -1002,16 +1002,16 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>232.24</v>
+        <v>533.2</v>
       </c>
       <c r="H12">
-        <v>312.85</v>
+        <v>791.22</v>
       </c>
       <c r="I12" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J12">
-        <v>80.61000000000001</v>
+        <v>258.02</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -1037,34 +1037,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B13" t="str">
-        <v>BM-5045</v>
+        <v>BM-5056</v>
       </c>
       <c r="C13" t="str">
-        <v>SAM-128GB-MID</v>
+        <v>IPH-64GB-MID</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000356355</v>
+        <v>350100000443464</v>
       </c>
       <c r="E13" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>237.5</v>
+        <v>194.75</v>
       </c>
       <c r="H13">
-        <v>306.63</v>
+        <v>250.75</v>
       </c>
       <c r="I13" t="str">
-        <v>Paypal</v>
+        <v>Card</v>
       </c>
       <c r="J13">
-        <v>69.13</v>
+        <v>56</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B14" t="str">
-        <v>BM-5049</v>
+        <v>BM-5061</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>SAM-128GB-WHI</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000388031</v>
+        <v>350100000483059</v>
       </c>
       <c r="E14" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>232.81</v>
+        <v>250.16</v>
       </c>
       <c r="H14">
-        <v>312.96</v>
+        <v>352.23</v>
       </c>
       <c r="I14" t="str">
-        <v>Klarna</v>
+        <v>Paypal</v>
       </c>
       <c r="J14">
-        <v>80.14999999999998</v>
+        <v>102.07000000000002</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v/>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1143,34 +1143,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B15" t="str">
-        <v>BM-5053</v>
+        <v>BM-5066</v>
       </c>
       <c r="C15" t="str">
-        <v>SAM-128GB-STA</v>
+        <v>IPH-128GB-BLA</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000419707</v>
+        <v>350100000522654</v>
       </c>
       <c r="E15" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>243.53</v>
+        <v>337.53</v>
       </c>
       <c r="H15">
-        <v>355.54</v>
+        <v>453.07</v>
       </c>
       <c r="I15" t="str">
-        <v>Card</v>
+        <v>Paypal</v>
       </c>
       <c r="J15">
-        <v>112.01000000000002</v>
+        <v>115.54000000000002</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1182,7 +1182,7 @@
         <v/>
       </c>
       <c r="N15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1196,16 +1196,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B16" t="str">
-        <v>BM-5057</v>
+        <v>BM-5071</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>GOO-128GB-BLU</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000451383</v>
+        <v>350100000562249</v>
       </c>
       <c r="E16" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -1214,16 +1214,16 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>218.51</v>
+        <v>264.82</v>
       </c>
       <c r="H16">
-        <v>289.95</v>
+        <v>382.77</v>
       </c>
       <c r="I16" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J16">
-        <v>71.44</v>
+        <v>117.94999999999999</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1249,16 +1249,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B17" t="str">
-        <v>BM-5061</v>
+        <v>BM-5076</v>
       </c>
       <c r="C17" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>IPH-256GB-STA</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000483059</v>
+        <v>350100000601844</v>
       </c>
       <c r="E17" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>250.16</v>
+        <v>476.5</v>
       </c>
       <c r="H17">
-        <v>347.92</v>
+        <v>605.3</v>
       </c>
       <c r="I17" t="str">
-        <v>Klarna</v>
+        <v>Paypal</v>
       </c>
       <c r="J17">
-        <v>97.76000000000002</v>
+        <v>128.79999999999995</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1302,16 +1302,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B18" t="str">
-        <v>BM-5065</v>
+        <v>BM-5081</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-128GB-PUR</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000514735</v>
+        <v>350100000641439</v>
       </c>
       <c r="E18" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -1320,16 +1320,16 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>222.24</v>
+        <v>231.07</v>
       </c>
       <c r="H18">
-        <v>312.92</v>
+        <v>317.79</v>
       </c>
       <c r="I18" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J18">
-        <v>90.68</v>
+        <v>86.72000000000003</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1355,16 +1355,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B19" t="str">
-        <v>BM-5069</v>
+        <v>BM-5086</v>
       </c>
       <c r="C19" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>SAM-256GB-GRA</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000546411</v>
+        <v>350100000681034</v>
       </c>
       <c r="E19" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -1373,16 +1373,16 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>263.11</v>
+        <v>413.46</v>
       </c>
       <c r="H19">
-        <v>367.36</v>
+        <v>533.81</v>
       </c>
       <c r="I19" t="str">
-        <v>Klarna</v>
+        <v>Card</v>
       </c>
       <c r="J19">
-        <v>104.25</v>
+        <v>120.34999999999997</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1408,16 +1408,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-20</v>
       </c>
       <c r="B20" t="str">
-        <v>BM-5073</v>
+        <v>BM-5091</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-128GB-MID</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000578087</v>
+        <v>350100007847729</v>
       </c>
       <c r="E20" t="str">
         <v>NORTHSIDE STOCK</v>
@@ -1426,16 +1426,16 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>222.91</v>
+        <v>530.25</v>
       </c>
       <c r="H20">
-        <v>318.37</v>
+        <v>746.88</v>
       </c>
       <c r="I20" t="str">
-        <v>Card</v>
+        <v>Klarna</v>
       </c>
       <c r="J20">
-        <v>95.46000000000001</v>
+        <v>216.63</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1461,16 +1461,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B21" t="str">
-        <v>BM-5077</v>
+        <v>BM-5096</v>
       </c>
       <c r="C21" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000609763</v>
+        <v>350100007887324</v>
       </c>
       <c r="E21" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -1479,16 +1479,16 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>257.31</v>
+        <v>223.04</v>
       </c>
       <c r="H21">
-        <v>363.2</v>
+        <v>298.35</v>
       </c>
       <c r="I21" t="str">
         <v>Klarna</v>
       </c>
       <c r="J21">
-        <v>105.88999999999999</v>
+        <v>75.31000000000003</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1512,274 +1512,9 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2026-07-10</v>
-      </c>
-      <c r="B22" t="str">
-        <v>BM-5081</v>
-      </c>
-      <c r="C22" t="str">
-        <v>IPH-128GB-PUR</v>
-      </c>
-      <c r="D22" t="str">
-        <v>350100000641439</v>
-      </c>
-      <c r="E22" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>231.07</v>
-      </c>
-      <c r="H22">
-        <v>293.53</v>
-      </c>
-      <c r="I22" t="str">
-        <v>Paypal</v>
-      </c>
-      <c r="J22">
-        <v>62.45999999999998</v>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22">
-        <v>8</v>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2026-07-14</v>
-      </c>
-      <c r="B23" t="str">
-        <v>BM-5085</v>
-      </c>
-      <c r="C23" t="str">
-        <v>SAM-128GB-GRA</v>
-      </c>
-      <c r="D23" t="str">
-        <v>350100000673115</v>
-      </c>
-      <c r="E23" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>246.21</v>
-      </c>
-      <c r="H23">
-        <v>352.53</v>
-      </c>
-      <c r="I23" t="str">
-        <v>Klarna</v>
-      </c>
-      <c r="J23">
-        <v>106.31999999999996</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23">
-        <v>6.3</v>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-18</v>
-      </c>
-      <c r="B24" t="str">
-        <v>BM-5089</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-128GB-MID</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100000704791</v>
-      </c>
-      <c r="E24" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>227.85</v>
-      </c>
-      <c r="H24">
-        <v>336.95</v>
-      </c>
-      <c r="I24" t="str">
-        <v>Klarna</v>
-      </c>
-      <c r="J24">
-        <v>109.1</v>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24">
-        <v>6.3</v>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="B25" t="str">
-        <v>BM-5093</v>
-      </c>
-      <c r="C25" t="str">
-        <v>SAM-128GB-MID</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007863567</v>
-      </c>
-      <c r="E25" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>242</v>
-      </c>
-      <c r="H25">
-        <v>356.32</v>
-      </c>
-      <c r="I25" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J25">
-        <v>114.32</v>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25">
-        <v>8</v>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-02</v>
-      </c>
-      <c r="B26" t="str">
-        <v>BM-5097</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007895243</v>
-      </c>
-      <c r="E26" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>223.04</v>
-      </c>
-      <c r="H26">
-        <v>314.16</v>
-      </c>
-      <c r="I26" t="str">
-        <v>Klarna</v>
-      </c>
-      <c r="J26">
-        <v>91.12000000000003</v>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26">
-        <v>8</v>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q21"/>
   </ignoredErrors>
 </worksheet>
 </file>